--- a/services/data_raw/eurostat/AT_lorries_road_eqr_lormot.xlsx
+++ b/services/data_raw/eurostat/AT_lorries_road_eqr_lormot.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,94 +417,94 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>freq</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>vehicle</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>mot_nrg</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>geo\TIME_PERIOD</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>2013</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>2014</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>2015</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>2016</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>2017</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>2018</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>2019</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>2020</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" t="n">
         <v>0</v>
       </c>
       <c r="B2" t="inlineStr">
@@ -582,7 +570,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" t="n">
         <v>1</v>
       </c>
       <c r="B3" t="inlineStr">
@@ -648,7 +636,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" t="n">
         <v>2</v>
       </c>
       <c r="B4" t="inlineStr">
@@ -668,7 +656,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Petroleum products [PET]</t>
+          <t>Petrol [PET]</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -714,7 +702,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" t="n">
         <v>3</v>
       </c>
       <c r="B5" t="inlineStr">
@@ -734,7 +722,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Petroleum products [PET]</t>
+          <t>Petrol [PET]</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -780,7 +768,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" t="n">
         <v>4</v>
       </c>
       <c r="B6" t="inlineStr">
@@ -846,7 +834,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" t="n">
         <v>5</v>
       </c>
       <c r="B7" t="inlineStr">
@@ -912,7 +900,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" t="n">
         <v>6</v>
       </c>
       <c r="B8" t="inlineStr">
@@ -978,7 +966,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" t="n">
         <v>7</v>
       </c>
       <c r="B9" t="inlineStr">
@@ -1044,7 +1032,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" t="n">
         <v>8</v>
       </c>
       <c r="B10" t="inlineStr">
@@ -1110,7 +1098,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" t="n">
         <v>9</v>
       </c>
       <c r="B11" t="inlineStr">
@@ -1176,7 +1164,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" t="n">
         <v>10</v>
       </c>
       <c r="B12" t="inlineStr">
@@ -1242,7 +1230,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" t="n">
         <v>11</v>
       </c>
       <c r="B13" t="inlineStr">
@@ -1308,7 +1296,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" t="n">
         <v>12</v>
       </c>
       <c r="B14" t="inlineStr">
@@ -1374,7 +1362,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" t="n">
         <v>13</v>
       </c>
       <c r="B15" t="inlineStr">
@@ -1440,7 +1428,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" t="n">
         <v>14</v>
       </c>
       <c r="B16" t="inlineStr">
@@ -1506,7 +1494,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" t="n">
         <v>15</v>
       </c>
       <c r="B17" t="inlineStr">
@@ -1572,7 +1560,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" t="n">
         <v>16</v>
       </c>
       <c r="B18" t="inlineStr">
@@ -1638,7 +1626,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" t="n">
         <v>17</v>
       </c>
       <c r="B19" t="inlineStr">
@@ -1704,7 +1692,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" t="n">
         <v>18</v>
       </c>
       <c r="B20" t="inlineStr">
@@ -1770,7 +1758,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" t="n">
         <v>19</v>
       </c>
       <c r="B21" t="inlineStr">
@@ -1836,7 +1824,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" t="n">
         <v>20</v>
       </c>
       <c r="B22" t="inlineStr">
@@ -1902,7 +1890,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" t="n">
         <v>21</v>
       </c>
       <c r="B23" t="inlineStr">
@@ -1968,7 +1956,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" t="n">
         <v>22</v>
       </c>
       <c r="B24" t="inlineStr">
@@ -2022,7 +2010,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" t="n">
         <v>23</v>
       </c>
       <c r="B25" t="inlineStr">
@@ -2076,7 +2064,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" t="n">
         <v>24</v>
       </c>
       <c r="B26" t="inlineStr">
@@ -2130,7 +2118,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" t="n">
         <v>25</v>
       </c>
       <c r="B27" t="inlineStr">
@@ -2184,7 +2172,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" t="n">
         <v>26</v>
       </c>
       <c r="B28" t="inlineStr">
@@ -2238,7 +2226,7 @@
       <c r="R28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" t="n">
         <v>27</v>
       </c>
       <c r="B29" t="inlineStr">
@@ -2292,7 +2280,7 @@
       <c r="R29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" t="n">
         <v>28</v>
       </c>
       <c r="B30" t="inlineStr">
@@ -2358,7 +2346,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" t="n">
         <v>29</v>
       </c>
       <c r="B31" t="inlineStr">

--- a/services/data_raw/eurostat/AT_lorries_road_eqr_lormot.xlsx
+++ b/services/data_raw/eurostat/AT_lorries_road_eqr_lormot.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R31"/>
+  <dimension ref="A1:S31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -502,6 +502,11 @@
           <t>2024</t>
         </is>
       </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -567,6 +572,9 @@
       </c>
       <c r="R2" t="n">
         <v>4447</v>
+      </c>
+      <c r="S2" t="n">
+        <v>3485</v>
       </c>
     </row>
     <row r="3">
@@ -634,6 +642,9 @@
       <c r="R3" t="n">
         <v>33088</v>
       </c>
+      <c r="S3" t="n">
+        <v>33451</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -700,6 +711,9 @@
       <c r="R4" t="n">
         <v>0</v>
       </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -766,6 +780,9 @@
       <c r="R5" t="n">
         <v>2169</v>
       </c>
+      <c r="S5" t="n">
+        <v>1570</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -788,7 +805,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Liquefied petroleum gases (LPG) [LPG]</t>
+          <t>Petrol (excluding hybrids) [PET_X_HYB]</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -812,7 +829,7 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -821,15 +838,18 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -854,7 +874,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Liquefied petroleum gases (LPG) [LPG]</t>
+          <t>Petrol (excluding hybrids) [PET_X_HYB]</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -863,40 +883,43 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>1280</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>1315</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1098</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1048</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1592</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2169</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>1800</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>988</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1532</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1255</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>1934</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2038</v>
+      </c>
+      <c r="S7" t="n">
+        <v>873</v>
       </c>
     </row>
     <row r="8">
@@ -920,7 +943,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Diesel [DIE]</t>
+          <t>Hybrid electric-petrol [ELC_PET_HYB]</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -929,40 +952,43 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>3463</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>3599</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>3508</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>4037</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>3948</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>4290</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>4603</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>3473</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>3678</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>3064</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>3719</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>4287</v>
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -986,7 +1012,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Diesel [DIE]</t>
+          <t>Hybrid electric-petrol [ELC_PET_HYB]</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -995,40 +1021,43 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>29004</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>29456</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>31334</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>34304</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>38242</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>40922</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>41030</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>34726</v>
+        <v>12</v>
       </c>
       <c r="O9" t="n">
-        <v>54803</v>
+        <v>19</v>
       </c>
       <c r="P9" t="n">
-        <v>18671</v>
+        <v>12</v>
       </c>
       <c r="Q9" t="n">
-        <v>25480</v>
+        <v>5</v>
       </c>
       <c r="R9" t="n">
-        <v>27984</v>
+        <v>131</v>
+      </c>
+      <c r="S9" t="n">
+        <v>108</v>
       </c>
     </row>
     <row r="10">
@@ -1052,7 +1081,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Natural gas [GAS]</t>
+          <t>Diesel [DIE]</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1061,40 +1090,43 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>7</v>
+        <v>3463</v>
       </c>
       <c r="H10" t="n">
-        <v>2</v>
+        <v>3599</v>
       </c>
       <c r="I10" t="n">
-        <v>3</v>
+        <v>3508</v>
       </c>
       <c r="J10" t="n">
-        <v>2</v>
+        <v>4037</v>
       </c>
       <c r="K10" t="n">
-        <v>5</v>
+        <v>3948</v>
       </c>
       <c r="L10" t="n">
-        <v>5</v>
+        <v>4290</v>
       </c>
       <c r="M10" t="n">
-        <v>12</v>
+        <v>4603</v>
       </c>
       <c r="N10" t="n">
-        <v>24</v>
+        <v>3473</v>
       </c>
       <c r="O10" t="n">
-        <v>37</v>
+        <v>3678</v>
       </c>
       <c r="P10" t="n">
-        <v>8</v>
+        <v>3064</v>
       </c>
       <c r="Q10" t="n">
-        <v>10</v>
+        <v>3719</v>
       </c>
       <c r="R10" t="n">
-        <v>27</v>
+        <v>4287</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3216</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1150,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Natural gas [GAS]</t>
+          <t>Diesel [DIE]</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1127,40 +1159,43 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>107</v>
+        <v>29004</v>
       </c>
       <c r="H11" t="n">
-        <v>112</v>
+        <v>29456</v>
       </c>
       <c r="I11" t="n">
-        <v>88</v>
+        <v>31334</v>
       </c>
       <c r="J11" t="n">
-        <v>50</v>
+        <v>34304</v>
       </c>
       <c r="K11" t="n">
-        <v>59</v>
+        <v>38242</v>
       </c>
       <c r="L11" t="n">
-        <v>75</v>
+        <v>40922</v>
       </c>
       <c r="M11" t="n">
-        <v>63</v>
+        <v>41030</v>
       </c>
       <c r="N11" t="n">
-        <v>43</v>
+        <v>34726</v>
       </c>
       <c r="O11" t="n">
-        <v>4</v>
+        <v>54803</v>
       </c>
       <c r="P11" t="n">
-        <v>49</v>
+        <v>18671</v>
       </c>
       <c r="Q11" t="n">
-        <v>2</v>
+        <v>25480</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>27984</v>
+      </c>
+      <c r="S11" t="n">
+        <v>27180</v>
       </c>
     </row>
     <row r="12">
@@ -1184,7 +1219,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Electricity [ELC]</t>
+          <t>Diesel (excluding hybrids) [DIE_X_HYB]</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1193,40 +1228,43 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>3463</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>3599</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>3508</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>4037</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>3948</v>
       </c>
       <c r="L12" t="n">
-        <v>10</v>
+        <v>4290</v>
       </c>
       <c r="M12" t="n">
-        <v>2</v>
+        <v>4603</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>3473</v>
       </c>
       <c r="O12" t="n">
-        <v>38</v>
+        <v>3678</v>
       </c>
       <c r="P12" t="n">
-        <v>57</v>
+        <v>3064</v>
       </c>
       <c r="Q12" t="n">
-        <v>43</v>
+        <v>3719</v>
       </c>
       <c r="R12" t="n">
-        <v>133</v>
+        <v>4287</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3216</v>
       </c>
     </row>
     <row r="13">
@@ -1250,7 +1288,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Electricity [ELC]</t>
+          <t>Diesel (excluding hybrids) [DIE_X_HYB]</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1259,40 +1297,43 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>191</v>
+        <v>29004</v>
       </c>
       <c r="H13" t="n">
-        <v>203</v>
+        <v>29456</v>
       </c>
       <c r="I13" t="n">
-        <v>267</v>
+        <v>31334</v>
       </c>
       <c r="J13" t="n">
-        <v>449</v>
+        <v>34304</v>
       </c>
       <c r="K13" t="n">
-        <v>237</v>
+        <v>38242</v>
       </c>
       <c r="L13" t="n">
-        <v>446</v>
+        <v>40922</v>
       </c>
       <c r="M13" t="n">
-        <v>500</v>
+        <v>41028</v>
       </c>
       <c r="N13" t="n">
-        <v>739</v>
+        <v>34704</v>
       </c>
       <c r="O13" t="n">
-        <v>2341</v>
+        <v>54558</v>
       </c>
       <c r="P13" t="n">
-        <v>2067</v>
+        <v>18399</v>
       </c>
       <c r="Q13" t="n">
-        <v>3265</v>
+        <v>25123</v>
       </c>
       <c r="R13" t="n">
-        <v>2928</v>
+        <v>27912</v>
+      </c>
+      <c r="S13" t="n">
+        <v>27024</v>
       </c>
     </row>
     <row r="14">
@@ -1316,7 +1357,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Alternative energy [ALT]</t>
+          <t>Hybrid diesel-electric [ELC_DIE_HYB]</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1325,40 +1366,43 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>160</v>
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1382,7 +1426,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Alternative energy [ALT]</t>
+          <t>Hybrid diesel-electric [ELC_DIE_HYB]</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1391,40 +1435,43 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>417</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>397</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>430</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>567</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>340</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>550</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>595</v>
+        <v>2</v>
       </c>
       <c r="N15" t="n">
-        <v>819</v>
+        <v>22</v>
       </c>
       <c r="O15" t="n">
-        <v>2451</v>
+        <v>245</v>
       </c>
       <c r="P15" t="n">
-        <v>2131</v>
+        <v>272</v>
       </c>
       <c r="Q15" t="n">
-        <v>3283</v>
+        <v>357</v>
       </c>
       <c r="R15" t="n">
-        <v>2935</v>
+        <v>72</v>
+      </c>
+      <c r="S15" t="n">
+        <v>156</v>
       </c>
     </row>
     <row r="16">
@@ -1448,7 +1495,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Petrol (excluding hybrids) [PET_X_HYB]</t>
+          <t>Alternative energy [ALT]</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1457,40 +1504,43 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L16" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O16" t="n">
-        <v>2</v>
+        <v>75</v>
       </c>
       <c r="P16" t="n">
-        <v>1</v>
+        <v>66</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>160</v>
+      </c>
+      <c r="S16" t="n">
+        <v>269</v>
       </c>
     </row>
     <row r="17">
@@ -1514,7 +1564,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Petrol (excluding hybrids) [PET_X_HYB]</t>
+          <t>Alternative energy [ALT]</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1523,40 +1573,43 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>1280</v>
+        <v>417</v>
       </c>
       <c r="H17" t="n">
-        <v>1315</v>
+        <v>397</v>
       </c>
       <c r="I17" t="n">
-        <v>1098</v>
+        <v>430</v>
       </c>
       <c r="J17" t="n">
-        <v>1048</v>
+        <v>567</v>
       </c>
       <c r="K17" t="n">
-        <v>1592</v>
+        <v>340</v>
       </c>
       <c r="L17" t="n">
-        <v>2169</v>
+        <v>550</v>
       </c>
       <c r="M17" t="n">
-        <v>1800</v>
+        <v>595</v>
       </c>
       <c r="N17" t="n">
-        <v>988</v>
+        <v>819</v>
       </c>
       <c r="O17" t="n">
-        <v>1532</v>
+        <v>2451</v>
       </c>
       <c r="P17" t="n">
-        <v>1255</v>
+        <v>2131</v>
       </c>
       <c r="Q17" t="n">
-        <v>1934</v>
+        <v>3283</v>
       </c>
       <c r="R17" t="n">
-        <v>2038</v>
+        <v>2935</v>
+      </c>
+      <c r="S17" t="n">
+        <v>4701</v>
       </c>
     </row>
     <row r="18">
@@ -1580,7 +1633,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hybrid electric-petrol [ELC_PET_HYB]</t>
+          <t>Electricity [ELC]</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1604,25 +1657,28 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>133</v>
+      </c>
+      <c r="S18" t="n">
+        <v>261</v>
       </c>
     </row>
     <row r="19">
@@ -1646,7 +1702,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Hybrid electric-petrol [ELC_PET_HYB]</t>
+          <t>Electricity [ELC]</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1655,40 +1711,43 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>191</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>203</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>267</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>449</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>237</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>446</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="N19" t="n">
-        <v>12</v>
+        <v>739</v>
       </c>
       <c r="O19" t="n">
-        <v>19</v>
+        <v>2341</v>
       </c>
       <c r="P19" t="n">
-        <v>12</v>
+        <v>2067</v>
       </c>
       <c r="Q19" t="n">
-        <v>5</v>
+        <v>3265</v>
       </c>
       <c r="R19" t="n">
-        <v>131</v>
+        <v>2928</v>
+      </c>
+      <c r="S19" t="n">
+        <v>4684</v>
       </c>
     </row>
     <row r="20">
@@ -1712,7 +1771,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Diesel (excluding hybrids) [DIE_X_HYB]</t>
+          <t>Bioethanol [BIOETH]</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1720,41 +1779,32 @@
           <t>AT</t>
         </is>
       </c>
-      <c r="G20" t="n">
-        <v>3463</v>
-      </c>
-      <c r="H20" t="n">
-        <v>3599</v>
-      </c>
-      <c r="I20" t="n">
-        <v>3508</v>
-      </c>
-      <c r="J20" t="n">
-        <v>4037</v>
-      </c>
-      <c r="K20" t="n">
-        <v>3948</v>
-      </c>
-      <c r="L20" t="n">
-        <v>4290</v>
-      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="M20" t="n">
-        <v>4603</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>3473</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>3678</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>3064</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>3719</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>4287</v>
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1778,7 +1828,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Diesel (excluding hybrids) [DIE_X_HYB]</t>
+          <t>Bioethanol [BIOETH]</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1786,41 +1836,32 @@
           <t>AT</t>
         </is>
       </c>
-      <c r="G21" t="n">
-        <v>29004</v>
-      </c>
-      <c r="H21" t="n">
-        <v>29456</v>
-      </c>
-      <c r="I21" t="n">
-        <v>31334</v>
-      </c>
-      <c r="J21" t="n">
-        <v>34304</v>
-      </c>
-      <c r="K21" t="n">
-        <v>38242</v>
-      </c>
-      <c r="L21" t="n">
-        <v>40922</v>
-      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="M21" t="n">
-        <v>41028</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>34704</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>54558</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>18399</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>25123</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>27912</v>
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1844,7 +1885,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Hybrid diesel-electric [ELC_DIE_HYB]</t>
+          <t>Biodiesel [BIODIE]</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1852,24 +1893,12 @@
           <t>AT</t>
         </is>
       </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
       <c r="M22" t="n">
         <v>0</v>
       </c>
@@ -1888,6 +1917,7 @@
       <c r="R22" t="n">
         <v>0</v>
       </c>
+      <c r="S22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1910,7 +1940,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Hybrid diesel-electric [ELC_DIE_HYB]</t>
+          <t>Biodiesel [BIODIE]</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1918,42 +1948,31 @@
           <t>AT</t>
         </is>
       </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
       <c r="M23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>245</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>272</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>357</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>72</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="S23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1976,7 +1995,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Bioethanol [BIOETH]</t>
+          <t>Natural gas [GAS]</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1984,29 +2003,44 @@
           <t>AT</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
+      <c r="G24" t="n">
+        <v>7</v>
+      </c>
+      <c r="H24" t="n">
+        <v>2</v>
+      </c>
+      <c r="I24" t="n">
+        <v>3</v>
+      </c>
+      <c r="J24" t="n">
+        <v>2</v>
+      </c>
+      <c r="K24" t="n">
+        <v>5</v>
+      </c>
+      <c r="L24" t="n">
+        <v>5</v>
+      </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>27</v>
+      </c>
+      <c r="S24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -2030,7 +2064,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Bioethanol [BIOETH]</t>
+          <t>Natural gas [GAS]</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2038,28 +2072,43 @@
           <t>AT</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
+      <c r="G25" t="n">
+        <v>107</v>
+      </c>
+      <c r="H25" t="n">
+        <v>112</v>
+      </c>
+      <c r="I25" t="n">
+        <v>88</v>
+      </c>
+      <c r="J25" t="n">
+        <v>50</v>
+      </c>
+      <c r="K25" t="n">
+        <v>59</v>
+      </c>
+      <c r="L25" t="n">
+        <v>75</v>
+      </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2084,7 +2133,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Biodiesel [BIODIE]</t>
+          <t>Compressed natural gas (CNG) [CNG]</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2092,30 +2141,31 @@
           <t>AT</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
-      <c r="R26" t="n">
-        <v>0</v>
-      </c>
+      <c r="G26" t="n">
+        <v>7</v>
+      </c>
+      <c r="H26" t="n">
+        <v>2</v>
+      </c>
+      <c r="I26" t="n">
+        <v>3</v>
+      </c>
+      <c r="J26" t="n">
+        <v>2</v>
+      </c>
+      <c r="K26" t="n">
+        <v>5</v>
+      </c>
+      <c r="L26" t="n">
+        <v>5</v>
+      </c>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -2138,7 +2188,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Biodiesel [BIODIE]</t>
+          <t>Compressed natural gas (CNG) [CNG]</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -2146,30 +2196,31 @@
           <t>AT</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
+      <c r="G27" t="n">
+        <v>107</v>
+      </c>
+      <c r="H27" t="n">
+        <v>112</v>
+      </c>
+      <c r="I27" t="n">
+        <v>88</v>
+      </c>
+      <c r="J27" t="n">
+        <v>50</v>
+      </c>
+      <c r="K27" t="n">
+        <v>59</v>
+      </c>
+      <c r="L27" t="n">
+        <v>75</v>
+      </c>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -2192,7 +2243,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Compressed natural gas (CNG) [CNG]</t>
+          <t>Liquefied petroleum gases (LPG) [LPG]</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2201,29 +2252,44 @@
         </is>
       </c>
       <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
         <v>7</v>
       </c>
-      <c r="H28" t="n">
-        <v>2</v>
-      </c>
-      <c r="I28" t="n">
-        <v>3</v>
-      </c>
-      <c r="J28" t="n">
-        <v>2</v>
-      </c>
-      <c r="K28" t="n">
-        <v>5</v>
-      </c>
-      <c r="L28" t="n">
-        <v>5</v>
-      </c>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr"/>
-      <c r="R28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -2246,7 +2312,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Compressed natural gas (CNG) [CNG]</t>
+          <t>Liquefied petroleum gases (LPG) [LPG]</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2255,29 +2321,44 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>107</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>112</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>88</v>
+        <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>75</v>
-      </c>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -2344,6 +2425,9 @@
       <c r="R30" t="n">
         <v>0</v>
       </c>
+      <c r="S30" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -2409,6 +2493,9 @@
       </c>
       <c r="R31" t="n">
         <v>7</v>
+      </c>
+      <c r="S31" t="n">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
